--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484192_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484192_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2851</v>
+        <v>1.2838</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9271</v>
+        <v>3.7675</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.642</v>
+        <v>-2.4837</v>
       </c>
       <c r="G2" t="n">
         <v>0.6627</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3248</v>
+        <v>1.3235</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8966</v>
+        <v>0.737</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4282</v>
+        <v>0.5865</v>
       </c>
       <c r="V2" t="n">
         <v>-2.2895</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. BONET TORRALBA</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7441</v>
+        <v>-0.1304</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4865</v>
+        <v>2.747</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2576</v>
+        <v>-2.8774</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4071</v>
+        <v>-2.2254</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.5592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4975</v>
+        <v>-1.6661</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4487</v>
+        <v>1.8384</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0887</v>
+        <v>1.9111</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.64</v>
+        <v>-0.0727</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8558</v>
+        <v>-4.0638</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9983</v>
+        <v>-2.4703</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1425</v>
+        <v>-1.5935</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3208</v>
+        <v>-1.2342</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9352</v>
+        <v>-0.9011</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6143</v>
+        <v>-0.3331</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2065</v>
+        <v>1.5437</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>E. ROMERO AGUERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-0.2076</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2765</v>
+        <v>-0.1269</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.1299</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.2254</v>
+        <v>-1.1244</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5592</v>
+        <v>0.2165</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6661</v>
+        <v>-1.3409</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8384</v>
+        <v>0.0658</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9111</v>
+        <v>0.746</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0727</v>
+        <v>-0.6802</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.0638</v>
+        <v>-1.1902</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4703</v>
+        <v>-0.5295</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5935</v>
+        <v>-0.6607</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9571</v>
+        <v>-0.2735</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3716</v>
+        <v>-0.1927</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5856</v>
+        <v>-0.0808</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5437</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. ROMERO AGUERA</t>
+          <t>B. BONET TORRALBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8971</v>
+        <v>-0.65</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.62</v>
+        <v>-0.0557</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2771</v>
+        <v>-0.5942</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1244</v>
+        <v>-0.4071</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2165</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3409</v>
+        <v>-0.4975</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0658</v>
+        <v>0.4487</v>
       </c>
       <c r="K5" t="n">
-        <v>0.746</v>
+        <v>1.0887</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6802</v>
+        <v>-0.64</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1902</v>
+        <v>-0.8558</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5295</v>
+        <v>-0.9983</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6607</v>
+        <v>0.1425</v>
       </c>
       <c r="P5" t="n">
         <v>1.1903</v>
@@ -844,22 +844,22 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.963</v>
+        <v>-0.2267</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6858</v>
+        <v>-0.5044</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2772</v>
+        <v>0.2777</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0337</v>
+        <v>-0.7174</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1044</v>
+        <v>0.3084</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1381</v>
+        <v>-1.0259</v>
       </c>
       <c r="G6" t="n">
         <v>0.2736</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.696</v>
+        <v>-0.3797</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5611</v>
+        <v>-0.357</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1349</v>
+        <v>-0.0227</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2065</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.421</v>
+        <v>-1.7434</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.0175</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7956</v>
+        <v>-1.7259</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.0739</v>
+        <v>-2.4804</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3829</v>
+        <v>1.5773</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.4568</v>
+        <v>-4.0577</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9017</v>
+        <v>0.8934</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6961000000000001</v>
+        <v>2.9691</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.5977</v>
+        <v>-2.0756</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1723</v>
+        <v>-3.3738</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3132</v>
+        <v>-1.3918</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.859</v>
+        <v>-1.9821</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>0.708</v>
+        <v>-0.8743</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9184</v>
+        <v>-0.7368</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2104</v>
+        <v>-0.1375</v>
       </c>
       <c r="V7" t="n">
-        <v>2.3417</v>
+        <v>1.8097</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3417</v>
+        <v>1.8097</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>A. OLMEDO GASCA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.637</v>
+        <v>-2.1379</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7147</v>
+        <v>-1.4428</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9223</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4804</v>
+        <v>-2.9877</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5773</v>
+        <v>-2.419</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.0577</v>
+        <v>-0.5688</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8934</v>
+        <v>-1.3174</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9691</v>
+        <v>-1.2797</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0756</v>
+        <v>-0.0376</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3738</v>
+        <v>-1.6704</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3918</v>
+        <v>-1.1392</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9821</v>
+        <v>-0.5312</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1984</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7679</v>
+        <v>-0.289</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4339</v>
+        <v>-0.34</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3339</v>
+        <v>0.051</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8097</v>
+        <v>0.9405</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8097</v>
+        <v>1.2065</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. OLMEDO GASCA</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6582</v>
+        <v>-2.2551</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.851</v>
+        <v>-1.5437</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8073</v>
+        <v>-0.7114</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9877</v>
+        <v>-4.0739</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.419</v>
+        <v>0.3829</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5688</v>
+        <v>-4.4568</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3174</v>
+        <v>-1.9017</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2797</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0376</v>
+        <v>-2.5977</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6704</v>
+        <v>-2.1723</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1392</v>
+        <v>-0.3132</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5312</v>
+        <v>-1.859</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8094</v>
+        <v>-0.1261</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7481</v>
+        <v>0.0001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0612</v>
+        <v>-0.1262</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9405</v>
+        <v>2.3417</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2065</v>
+        <v>2.3417</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7149</v>
+        <v>-2.5287</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9629</v>
+        <v>-0.8609</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7519</v>
+        <v>-1.6678</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1329</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.59</v>
+        <v>-0.4038</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3741</v>
+        <v>-0.272</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.216</v>
+        <v>-0.1318</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9754</v>
+        <v>-3.8453</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8849</v>
+        <v>-1.7829</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0905</v>
+        <v>-2.0624</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5577</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4096</v>
+        <v>-1.2795</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1222</v>
+        <v>-1.0202</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2874</v>
+        <v>-0.2594</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3972</v>
+        <v>-4.5481</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8698</v>
+        <v>-1.1329</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5274</v>
+        <v>-3.4152</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8858</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6143</v>
+        <v>-0.7652</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4963</v>
+        <v>-0.7594</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.118</v>
+        <v>-0.0057</v>
       </c>
       <c r="V12" t="n">
         <v>-1.881</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5406</v>
+        <v>-7.1721</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5399</v>
+        <v>-3.1714</v>
       </c>
       <c r="F13" t="n">
         <v>-4.0007</v>
@@ -1468,10 +1468,10 @@
         <v>0.9919</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2526</v>
+        <v>-0.8842</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1222</v>
+        <v>-0.7538</v>
       </c>
       <c r="U13" t="n">
         <v>-0.1304</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-25.5874</v>
+        <v>-24.6522</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2472</v>
+        <v>-3.3118</v>
       </c>
       <c r="F14" t="n">
         <v>-21.3404</v>
@@ -1546,16 +1546,16 @@
         <v>14.8789</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.347900000000001</v>
+        <v>-5.4127</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.0355</v>
+        <v>-5.100300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3124999999999999</v>
+        <v>-0.3124</v>
       </c>
       <c r="V14" t="n">
-        <v>0.05210000000000026</v>
+        <v>0.05210000000000048</v>
       </c>
       <c r="W14" t="n">
         <v>5.4101</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1093</v>
+        <v>5.4563</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3453</v>
+        <v>4.1412</v>
       </c>
       <c r="F15" t="n">
-        <v>1.764</v>
+        <v>1.3151</v>
       </c>
       <c r="G15" t="n">
         <v>2.4677</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1574</v>
+        <v>0.5044</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0284</v>
+        <v>-0.1756</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1289</v>
+        <v>0.68</v>
       </c>
       <c r="V15" t="n">
         <v>2.4842</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5193</v>
+        <v>5.2641</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8882</v>
+        <v>4.2963</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6311</v>
+        <v>0.9677</v>
       </c>
       <c r="G16" t="n">
         <v>4.9523</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3605</v>
+        <v>1.1053</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1757</v>
+        <v>0.2324</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5362</v>
+        <v>0.8728</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TARRIDA TORRES</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2389</v>
+        <v>3.8753</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0745</v>
+        <v>3.4302</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1645</v>
+        <v>0.445</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6244</v>
+        <v>1.7765</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4949</v>
+        <v>-0.2018</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8706</v>
+        <v>1.9784</v>
       </c>
       <c r="J17" t="n">
-        <v>2.782</v>
+        <v>2.0768</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8211</v>
+        <v>0.7916</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0391</v>
+        <v>1.2852</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1576</v>
+        <v>-0.3002</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3262</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1685</v>
+        <v>0.6932</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6226</v>
+        <v>0.2295</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4908</v>
+        <v>-0.119</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1318</v>
+        <v>0.3485</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6032</v>
+        <v>1.4724</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.6385</v>
+        <v>3.4905</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7151</v>
+        <v>2.5111</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9234</v>
+        <v>0.9795</v>
       </c>
       <c r="G18" t="n">
         <v>2.0763</v>
@@ -1858,13 +1858,13 @@
         <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>0.967</v>
+        <v>0.819</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4025</v>
+        <v>0.1985</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5645</v>
+        <v>0.6206</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>A. TARRIDA TORRES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4009</v>
+        <v>3.1906</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1241</v>
+        <v>3.0542</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2767</v>
+        <v>0.1364</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7765</v>
+        <v>1.6244</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2018</v>
+        <v>2.4949</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9784</v>
+        <v>-0.8706</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0768</v>
+        <v>2.782</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7916</v>
+        <v>3.8211</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2852</v>
+        <v>-1.0391</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3002</v>
+        <v>-1.1576</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-1.3262</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6932</v>
+        <v>0.1685</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2449</v>
+        <v>1.5743</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4251</v>
+        <v>0.4705</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1802</v>
+        <v>1.1038</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4724</v>
+        <v>-0.6032</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5409</v>
+        <v>1.99</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0611</v>
+        <v>0.9591</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4798</v>
+        <v>1.0309</v>
       </c>
       <c r="G20" t="n">
         <v>4.3901</v>
@@ -2014,13 +2014,13 @@
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3331</v>
+        <v>0.7822</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2155</v>
+        <v>0.1135</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1176</v>
+        <v>0.6687</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6032</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7574</v>
+        <v>1.9156</v>
       </c>
       <c r="E21" t="n">
-        <v>3.5656</v>
+        <v>3.6677</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8082</v>
+        <v>-1.7521</v>
       </c>
       <c r="G21" t="n">
         <v>4.5136</v>
@@ -2092,13 +2092,13 @@
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0374</v>
+        <v>0.1955</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4137</v>
+        <v>-0.3117</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4511</v>
+        <v>0.5072</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3066</v>
+        <v>1.7351</v>
       </c>
       <c r="E22" t="n">
-        <v>1.324</v>
+        <v>1.5281</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0174</v>
+        <v>0.207</v>
       </c>
       <c r="G22" t="n">
         <v>0.9525</v>
@@ -2170,13 +2170,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.3401</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4024</v>
+        <v>-0.1983</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3662</v>
+        <v>-0.1418</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3051</v>
+        <v>0.4888</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.715</v>
+        <v>-0.3069</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0201</v>
+        <v>0.7957</v>
       </c>
       <c r="G23" t="n">
         <v>1.0722</v>
@@ -2248,13 +2248,13 @@
         <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8875</v>
+        <v>1.0712</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.238</v>
+        <v>0.1701</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1256</v>
+        <v>0.9011</v>
       </c>
       <c r="V23" t="n">
         <v>-0.266</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.007</v>
+        <v>0.1435</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5289</v>
+        <v>0.4269</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5359</v>
+        <v>-0.2834</v>
       </c>
       <c r="G24" t="n">
         <v>1.8182</v>
@@ -2326,13 +2326,13 @@
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2307</v>
+        <v>0.3811</v>
       </c>
       <c r="T24" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.0339</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1626</v>
+        <v>0.4151</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0639</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2224</v>
+        <v>-1.9623</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5716</v>
+        <v>-2.3676</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3492</v>
+        <v>0.4053</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4007</v>
@@ -2404,13 +2404,13 @@
         <v>0.3968</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2347</v>
+        <v>0.0255</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.238</v>
+        <v>-0.034</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0034</v>
+        <v>0.0595</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2440,10 +2440,10 @@
         <v>25.5875</v>
       </c>
       <c r="E26" t="n">
-        <v>21.3402</v>
+        <v>21.3403</v>
       </c>
       <c r="F26" t="n">
-        <v>4.2473</v>
+        <v>4.247100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>25.2431</v>
@@ -2482,19 +2482,19 @@
         <v>8.9274</v>
       </c>
       <c r="S26" t="n">
-        <v>6.348</v>
+        <v>6.3479</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3124</v>
+        <v>0.3125</v>
       </c>
       <c r="U26" t="n">
-        <v>6.0357</v>
+        <v>6.0355</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.05220000000000002</v>
+        <v>-0.0521999999999998</v>
       </c>
       <c r="W26" t="n">
-        <v>5.357799999999999</v>
+        <v>5.3578</v>
       </c>
       <c r="X26" t="n">
         <v>-5.4099</v>
